--- a/INSTANCES/instances_xlsx/A_MTN_5/231FL_10A_3.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/231FL_10A_3.xlsx
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -7772,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
